--- a/experiments/lora_finetuning/epoch_ablation/report/epoch_ablation.xlsx
+++ b/experiments/lora_finetuning/epoch_ablation/report/epoch_ablation.xlsx
@@ -563,19 +563,19 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -626,17 +626,17 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Term Acc (%)</t>
+          <t>Term Accuracy %</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Cons Macro Avg</t>
+          <t>Macro Consistency</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Cons Weighted Avg</t>
+          <t>Weighted Consistency</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -651,17 +651,17 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Term Acc (%)</t>
+          <t>Term Accuracy %</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>Cons Macro Avg</t>
+          <t>Macro Consistency</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Cons Weighted Avg</t>
+          <t>Weighted Consistency</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -676,17 +676,17 @@
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>Term Acc (%)</t>
+          <t>Term Accuracy %</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>Cons Macro Avg</t>
+          <t>Macro Consistency</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>Cons Weighted Avg</t>
+          <t>Weighted Consistency</t>
         </is>
       </c>
     </row>
@@ -869,19 +869,19 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -932,17 +932,17 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Term Acc (%)</t>
+          <t>Term Accuracy %</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Cons Macro Avg</t>
+          <t>Macro Consistency</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Cons Weighted Avg</t>
+          <t>Weighted Consistency</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Term Acc (%)</t>
+          <t>Term Accuracy %</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>Cons Macro Avg</t>
+          <t>Macro Consistency</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Cons Weighted Avg</t>
+          <t>Weighted Consistency</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -982,17 +982,17 @@
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>Term Acc (%)</t>
+          <t>Term Accuracy %</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>Cons Macro Avg</t>
+          <t>Macro Consistency</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>Cons Weighted Avg</t>
+          <t>Weighted Consistency</t>
         </is>
       </c>
     </row>
